--- a/cases/CASE-002/raw/Зенченко Динамика производства.xlsx
+++ b/cases/CASE-002/raw/Зенченко Динамика производства.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\asus\IWE\PACK-cattle-science\cases\CASE-002\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31941127-4FA3-4223-BC85-8378DFE7F3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACF3953-3C87-49E3-B7AC-C5D7D229827A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="7">
   <si>
     <t>Ж/К №1</t>
   </si>
@@ -278,10 +278,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{282AE3F9-C4C0-4370-BF5B-1216F82693F9}" name="Таблица1" displayName="Таблица1" ref="A2:E52" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
-  <autoFilter ref="A2:E52" xr:uid="{282AE3F9-C4C0-4370-BF5B-1216F82693F9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E52">
-    <sortCondition descending="1" ref="A2:A52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{282AE3F9-C4C0-4370-BF5B-1216F82693F9}" name="Таблица1" displayName="Таблица1" ref="A2:E54" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="A2:E54" xr:uid="{282AE3F9-C4C0-4370-BF5B-1216F82693F9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E54">
+    <sortCondition descending="1" ref="A2:A54"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{6C7FA057-1199-422A-B8F5-B38BBD80CBFA}" name="Дата" dataDxfId="4"/>
@@ -559,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E52"/>
+  <dimension ref="A2:E54"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.7265625" style="1" customWidth="1"/>
@@ -595,25 +595,25 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D3" s="2">
-        <v>18324</v>
+        <v>18457</v>
       </c>
       <c r="E3" s="7">
         <f>D3/C3</f>
-        <v>32.89766606822262</v>
+        <v>32.958928571428572</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>1</v>
@@ -622,52 +622,52 @@
         <v>851</v>
       </c>
       <c r="D4" s="2">
-        <v>26876</v>
+        <v>26923</v>
       </c>
       <c r="E4" s="7">
         <f>D4/C4</f>
-        <v>31.581668625146886</v>
+        <v>31.636897767332549</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
-        <v>46209</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3">
-        <v>851</v>
-      </c>
-      <c r="D5" s="3">
-        <v>27894</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="A5" s="5">
+        <v>46211</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>557</v>
+      </c>
+      <c r="D5" s="2">
+        <v>18324</v>
+      </c>
+      <c r="E5" s="7">
         <f>D5/C5</f>
-        <v>32.777908343125738</v>
+        <v>32.89766606822262</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2">
-        <v>551</v>
+        <v>851</v>
       </c>
       <c r="D6" s="2">
-        <v>18026</v>
+        <v>26876</v>
       </c>
       <c r="E6" s="7">
         <f>D6/C6</f>
-        <v>32.715063520871141</v>
+        <v>31.581668625146886</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>1</v>
@@ -676,29 +676,29 @@
         <v>851</v>
       </c>
       <c r="D7" s="3">
-        <v>27928</v>
+        <v>27894</v>
       </c>
       <c r="E7" s="6">
         <f>D7/C7</f>
-        <v>32.817861339600469</v>
+        <v>32.777908343125738</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C8" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D8" s="2">
-        <v>17952</v>
+        <v>18026</v>
       </c>
       <c r="E8" s="7">
         <f>D8/C8</f>
-        <v>32.819012797074954</v>
+        <v>32.715063520871141</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -739,38 +739,38 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>46205</v>
+        <v>46208</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="3">
-        <v>538</v>
+        <v>851</v>
       </c>
       <c r="D11" s="3">
-        <v>17221</v>
+        <v>27928</v>
       </c>
       <c r="E11" s="6">
         <f>D11/C11</f>
-        <v>32.009293680297397</v>
+        <v>32.817861339600469</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
-        <v>46205</v>
+        <v>46208</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="2">
-        <v>851</v>
+        <v>547</v>
       </c>
       <c r="D12" s="2">
-        <v>27899</v>
+        <v>17952</v>
       </c>
       <c r="E12" s="7">
         <f>D12/C12</f>
-        <v>32.783783783783782</v>
+        <v>32.819012797074954</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -778,17 +778,17 @@
         <v>46205</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="3">
-        <v>851</v>
+        <v>538</v>
       </c>
       <c r="D13" s="3">
-        <v>27899</v>
+        <v>17221</v>
       </c>
       <c r="E13" s="6">
         <f>D13/C13</f>
-        <v>32.783783783783782</v>
+        <v>32.009293680297397</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -796,53 +796,53 @@
         <v>46205</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2">
-        <v>538</v>
+        <v>851</v>
       </c>
       <c r="D14" s="2">
-        <v>17221</v>
+        <v>27899</v>
       </c>
       <c r="E14" s="7">
         <f>D14/C14</f>
-        <v>32.009293680297397</v>
+        <v>32.783783783783782</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="3">
-        <v>532</v>
+        <v>851</v>
       </c>
       <c r="D15" s="3">
-        <v>16731</v>
+        <v>27899</v>
       </c>
       <c r="E15" s="6">
         <f>D15/C15</f>
-        <v>31.449248120300751</v>
+        <v>32.783783783783782</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="2">
-        <v>871</v>
+        <v>538</v>
       </c>
       <c r="D16" s="2">
-        <v>27269</v>
+        <v>17221</v>
       </c>
       <c r="E16" s="7">
         <f>D16/C16</f>
-        <v>31.307692307692307</v>
+        <v>32.009293680297397</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -850,17 +850,17 @@
         <v>46204</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="3">
-        <v>871</v>
+        <v>532</v>
       </c>
       <c r="D17" s="3">
-        <v>27269</v>
+        <v>16731</v>
       </c>
       <c r="E17" s="6">
         <f>D17/C17</f>
-        <v>31.307692307692307</v>
+        <v>31.449248120300751</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -868,22 +868,22 @@
         <v>46204</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" s="2">
-        <v>532</v>
+        <v>871</v>
       </c>
       <c r="D18" s="2">
-        <v>16731</v>
+        <v>27269</v>
       </c>
       <c r="E18" s="7">
         <f>D18/C18</f>
-        <v>31.449248120300751</v>
+        <v>31.307692307692307</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>1</v>
@@ -892,34 +892,34 @@
         <v>871</v>
       </c>
       <c r="D19" s="3">
-        <v>27496</v>
+        <v>27269</v>
       </c>
       <c r="E19" s="6">
         <f>D19/C19</f>
-        <v>31.568312284730194</v>
+        <v>31.307692307692307</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C20" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D20" s="2">
-        <v>16944</v>
+        <v>16731</v>
       </c>
       <c r="E20" s="7">
         <f>D20/C20</f>
-        <v>31.969811320754715</v>
+        <v>31.449248120300751</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>1</v>
@@ -928,142 +928,142 @@
         <v>871</v>
       </c>
       <c r="D21" s="3">
-        <v>26937</v>
+        <v>27496</v>
       </c>
       <c r="E21" s="6">
         <f>D21/C21</f>
-        <v>30.926521239954077</v>
+        <v>31.568312284730194</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C22" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D22" s="2">
-        <v>16983</v>
+        <v>16944</v>
       </c>
       <c r="E22" s="7">
         <f>D22/C22</f>
-        <v>32.103969754253306</v>
+        <v>31.969811320754715</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C23" s="3">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D23" s="3">
-        <v>26407</v>
+        <v>26937</v>
       </c>
       <c r="E23" s="6">
         <f>D23/C23</f>
-        <v>30.352873563218392</v>
+        <v>30.926521239954077</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C24" s="2">
-        <v>550</v>
+        <v>529</v>
       </c>
       <c r="D24" s="2">
-        <v>16633</v>
+        <v>16983</v>
       </c>
       <c r="E24" s="7">
         <f>D24/C24</f>
-        <v>30.241818181818182</v>
+        <v>32.103969754253306</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C25" s="3">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="D25" s="3">
-        <v>26315</v>
+        <v>26407</v>
       </c>
       <c r="E25" s="6">
         <f>D25/C25</f>
-        <v>30.421965317919074</v>
+        <v>30.352873563218392</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C26" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="D26" s="2">
-        <v>17025</v>
+        <v>16633</v>
       </c>
       <c r="E26" s="7">
         <f>D26/C26</f>
-        <v>31.411439114391143</v>
+        <v>30.241818181818182</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C27" s="3">
-        <v>880</v>
+        <v>865</v>
       </c>
       <c r="D27" s="3">
-        <v>26355</v>
+        <v>26315</v>
       </c>
       <c r="E27" s="6">
         <f>D27/C27</f>
-        <v>29.948863636363637</v>
+        <v>30.421965317919074</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C28" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D28" s="2">
-        <v>16565</v>
+        <v>17025</v>
       </c>
       <c r="E28" s="7">
         <f>D28/C28</f>
-        <v>30.675925925925927</v>
+        <v>31.411439114391143</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>1</v>
@@ -1072,106 +1072,106 @@
         <v>880</v>
       </c>
       <c r="D29" s="3">
-        <v>25697</v>
+        <v>26355</v>
       </c>
       <c r="E29" s="6">
         <f>D29/C29</f>
-        <v>29.201136363636362</v>
+        <v>29.948863636363637</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C30" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D30" s="2">
-        <v>16723</v>
+        <v>16565</v>
       </c>
       <c r="E30" s="7">
         <f>D30/C30</f>
-        <v>31.08364312267658</v>
+        <v>30.675925925925927</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
-        <v>46194</v>
+        <v>46196</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" s="3">
-        <v>533</v>
+        <v>880</v>
       </c>
       <c r="D31" s="3">
-        <v>16644</v>
+        <v>25697</v>
       </c>
       <c r="E31" s="6">
         <f>D31/C31</f>
-        <v>31.227016885553471</v>
+        <v>29.201136363636362</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
-        <v>46194</v>
+        <v>46196</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" s="2">
-        <v>876</v>
+        <v>538</v>
       </c>
       <c r="D32" s="2">
-        <v>25396</v>
+        <v>16723</v>
       </c>
       <c r="E32" s="7">
         <f>D32/C32</f>
-        <v>28.990867579908677</v>
+        <v>31.08364312267658</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
-        <v>46192</v>
+        <v>46194</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C33" s="3">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D33" s="3">
-        <v>16804</v>
+        <v>16644</v>
       </c>
       <c r="E33" s="6">
         <f>D33/C33</f>
-        <v>31.645951035781543</v>
+        <v>31.227016885553471</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
-        <v>46192</v>
+        <v>46194</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="2">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="D34" s="2">
-        <v>26396</v>
+        <v>25396</v>
       </c>
       <c r="E34" s="7">
         <f>D34/C34</f>
-        <v>30.340229885057472</v>
+        <v>28.990867579908677</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>0</v>
@@ -1180,178 +1180,178 @@
         <v>531</v>
       </c>
       <c r="D35" s="3">
-        <v>16811</v>
+        <v>16804</v>
       </c>
       <c r="E35" s="6">
         <f>D35/C35</f>
-        <v>31.659133709981166</v>
+        <v>31.645951035781543</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C36" s="2">
-        <v>859</v>
+        <v>870</v>
       </c>
       <c r="D36" s="2">
-        <v>27534</v>
+        <v>26396</v>
       </c>
       <c r="E36" s="7">
         <f>D36/C36</f>
-        <v>32.053550640279397</v>
+        <v>30.340229885057472</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C37" s="3">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="D37" s="3">
-        <v>17426</v>
+        <v>16811</v>
       </c>
       <c r="E37" s="6">
         <f>D37/C37</f>
-        <v>31.799270072992702</v>
+        <v>31.659133709981166</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C38" s="2">
-        <v>882</v>
+        <v>859</v>
       </c>
       <c r="D38" s="2">
-        <v>27254</v>
+        <v>27534</v>
       </c>
       <c r="E38" s="7">
         <f>D38/C38</f>
-        <v>30.900226757369616</v>
+        <v>32.053550640279397</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
-        <v>46187</v>
+        <v>46190</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C39" s="3">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D39" s="3">
-        <v>17383</v>
+        <v>17426</v>
       </c>
       <c r="E39" s="6">
         <f>D39/C39</f>
-        <v>32.071955719557195</v>
+        <v>31.799270072992702</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
-        <v>46187</v>
+        <v>46190</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C40" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D40" s="2">
-        <v>26337</v>
+        <v>27254</v>
       </c>
       <c r="E40" s="7">
         <f>D40/C40</f>
-        <v>29.894438138479</v>
+        <v>30.900226757369616</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C41" s="3">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D41" s="3">
-        <v>17198</v>
+        <v>17383</v>
       </c>
       <c r="E41" s="6">
         <f>D41/C41</f>
-        <v>31.848148148148148</v>
+        <v>32.071955719557195</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C42" s="2">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D42" s="2">
-        <v>26182</v>
+        <v>26337</v>
       </c>
       <c r="E42" s="7">
         <f>D42/C42</f>
-        <v>29.684807256235828</v>
+        <v>29.894438138479</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C43" s="3">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="D43" s="3">
-        <v>16902</v>
+        <v>17198</v>
       </c>
       <c r="E43" s="6">
         <f>D43/C43</f>
-        <v>31.890566037735848</v>
+        <v>31.848148148148148</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C44" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D44" s="2">
-        <v>26018</v>
+        <v>26182</v>
       </c>
       <c r="E44" s="7">
         <f>D44/C44</f>
-        <v>29.565909090909091</v>
+        <v>29.684807256235828</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>0</v>
@@ -1360,136 +1360,172 @@
         <v>530</v>
       </c>
       <c r="D45" s="3">
-        <v>16891</v>
+        <v>16902</v>
       </c>
       <c r="E45" s="6">
         <f>D45/C45</f>
-        <v>31.869811320754717</v>
+        <v>31.890566037735848</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C46" s="2">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="D46" s="2">
-        <v>26089</v>
+        <v>26018</v>
       </c>
       <c r="E46" s="7">
         <f>D46/C46</f>
-        <v>29.74800456100342</v>
+        <v>29.565909090909091</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C47" s="3">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="D47" s="3">
-        <v>17021</v>
+        <v>16891</v>
       </c>
       <c r="E47" s="6">
         <f>D47/C47</f>
-        <v>32.420952380952379</v>
+        <v>31.869811320754717</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C48" s="2">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="D48" s="2">
-        <v>24359</v>
+        <v>26089</v>
       </c>
       <c r="E48" s="7">
         <f>D48/C48</f>
-        <v>28.031070195627159</v>
+        <v>29.74800456100342</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
-        <v>46164</v>
+        <v>46181</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C49" s="3">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D49" s="3">
-        <v>16424</v>
+        <v>17021</v>
       </c>
       <c r="E49" s="6">
         <f>D49/C49</f>
-        <v>31.34351145038168</v>
+        <v>32.420952380952379</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
-        <v>46164</v>
+        <v>46181</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C50" s="2">
-        <v>820</v>
+        <v>869</v>
       </c>
       <c r="D50" s="2">
-        <v>24296</v>
+        <v>24359</v>
       </c>
       <c r="E50" s="7">
         <f>D50/C50</f>
-        <v>29.629268292682926</v>
+        <v>28.031070195627159</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
-        <v>46144</v>
+        <v>46164</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C51" s="3">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="D51" s="3">
-        <v>16355</v>
+        <v>16424</v>
       </c>
       <c r="E51" s="6">
         <f>D51/C51</f>
-        <v>31.757281553398059</v>
+        <v>31.34351145038168</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
-        <v>46144</v>
+        <v>46164</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C52" s="2">
-        <v>764</v>
+        <v>820</v>
       </c>
       <c r="D52" s="2">
-        <v>22185</v>
+        <v>24296</v>
       </c>
       <c r="E52" s="7">
         <f>D52/C52</f>
+        <v>29.629268292682926</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3">
+        <v>515</v>
+      </c>
+      <c r="D53" s="3">
+        <v>16355</v>
+      </c>
+      <c r="E53" s="6">
+        <f>D53/C53</f>
+        <v>31.757281553398059</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="5">
+        <v>46144</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2">
+        <v>764</v>
+      </c>
+      <c r="D54" s="2">
+        <v>22185</v>
+      </c>
+      <c r="E54" s="7">
+        <f>D54/C54</f>
         <v>29.037958115183248</v>
       </c>
     </row>
@@ -1505,7 +1541,7 @@
           <x14:formula1>
             <xm:f>Лист2!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>B3:B52</xm:sqref>
+          <xm:sqref>B3:B54</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
